--- a/docs/perechen-otchetov/obrazcy/ФО-04.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-04.xlsx
@@ -3311,7 +3311,7 @@
       </c>
       <c r="B14" s="44" t="inlineStr">
         <is>
-          <t>Строка детали — платёж: номер платёжного документа («п/п 4372»), дата платежа и вид погашения. В отчёт попадают платежи с датой поступления в периоде, засчитанные в погашение так же, как в расчёте кредита: подтверждённые Центральным казначейством, восстановленные, с расхождением — по сумме ЦК, поступившие через шлюз и ещё ожидающие подтверждения. Сторнированные и внесённые вручную или импортом, но не подтверждённые ЦК, не входят. Дата платежа — дата фактического поступления денег: поступление, опознанное позже, ложится в свой день, поэтому до закрытия периода отчёт за него может меняться. Принятие имущества в счёт погашения — платёж с этим видом погашения. Не погашения и в отчёт не входят: списание (ФО-11), перевод долга (ФО-12), доля залогодателя в выручке от реализации залога, невыясненные поступления, возврат переплаты. «Всего погашено» = основная сумма + проценты (вместе с накопленными) + штрафы; доля платежа на расходы по взысканию в отчёт не входит. Над платежами разрезы, по умолчанию область → район → заёмщик → кредит; строка кредита («№ … от …, KGS») есть всегда, даже при одном платеже; у городов республиканского значения — обе строки, области и района. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Порядок: области — по справочнику (области по алфавиту, затем г. Бишкек, г. Ош); районы — по алфавиту; заёмщики — по алфавиту; кредиты заёмщика — по дате договора; платежи кредита — по дате платежа, от ранних к поздним. Суммы — только в сомах (тыс. сом), в том числе по кредитам в иностранной валюте: погашения приходят в сомах, в валюту договора их пересчитывает расчёт задолженности; строки в валюте нет. Колонок сравнения с другими периодами нет: с начала года — выбором периода, помесячно — разрезом «Месяц». Печать — A4 альбомная в одну страницу по ширине.</t>
+          <t>Строка детали — платёж: номер платёжного документа («п/п 4372»), дата платежа и вид погашения. В отчёт попадают платежи с датой поступления в периоде, засчитанные в погашение так же, как в расчёте кредита: подтверждённые Центральным казначейством, восстановленные, с расхождением — по сумме ЦК, поступившие через шлюз и ещё ожидающие подтверждения. Сторнированные и внесённые вручную или импортом, но не подтверждённые ЦК, не входят. Дата платежа — дата фактического поступления денег: поступление, опознанное позже, ложится в свой день, поэтому до закрытия периода отчёт за него может меняться. Принятие имущества в счёт погашения — платёж с этим видом погашения. Не погашения и в отчёт не входят: списание (ФО-11), перевод долга, доля залогодателя в выручке от реализации залога, невыясненные поступления, возврат переплаты. «Всего погашено» = основная сумма + проценты (вместе с накопленными) + штрафы; доля платежа на расходы по взысканию в отчёт не входит. Над платежами разрезы, по умолчанию область → район → заёмщик → кредит; строка кредита («№ … от …, KGS») есть всегда, даже при одном платеже; у городов республиканского значения — обе строки, области и района. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Порядок: области — по справочнику (области по алфавиту, затем г. Бишкек, г. Ош); районы — по алфавиту; заёмщики — по алфавиту; кредиты заёмщика — по дате договора; платежи кредита — по дате платежа, от ранних к поздним. Суммы — только в сомах (тыс. сом), в том числе по кредитам в иностранной валюте: погашения приходят в сомах, в валюту договора их пересчитывает расчёт задолженности; строки в валюте нет. Колонок сравнения с другими периодами нет: с начала года — выбором периода, помесячно — разрезом «Месяц». Печать — A4 альбомная в одну страницу по ширине.</t>
         </is>
       </c>
     </row>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="B40" s="44" t="inlineStr">
         <is>
-          <t>Платёж КЗ-07 от 02.09.2026 показан; перевод его долга 09.09.2026 (ФО-12) и списание КЗ-08 17.09.2026 (ФО-11) — не платежи и не показаны.</t>
+          <t>Платёж КЗ-07 от 02.09.2026 показан; перевод его долга 09.09.2026 и списание КЗ-08 17.09.2026 (ФО-11) — не платежи и не показаны.</t>
         </is>
       </c>
     </row>

--- a/docs/perechen-otchetov/obrazcy/ФО-04.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-04.xlsx
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -805,22 +805,22 @@
       <c r="B8" s="7" t="n"/>
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>1667.91</v>
+        <v>1706.0772</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>1467</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>200.91</v>
+        <v>239.0772</v>
       </c>
       <c r="J8" s="9" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
     <row r="20" ht="13" customHeight="1">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>ОсОО «Эко-Продукт»</t>
+          <t>ОсОО «Ысык-Көл Логистик»</t>
         </is>
       </c>
       <c r="B20" s="20" t="n"/>
@@ -1381,22 +1381,22 @@
       <c r="B28" s="11" t="n"/>
       <c r="C28" s="10" t="n"/>
       <c r="D28" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" s="13" t="n">
-        <v>464.375</v>
+        <v>502.5422</v>
       </c>
       <c r="H28" s="13" t="n">
         <v>380</v>
       </c>
       <c r="I28" s="13" t="n">
-        <v>84.375</v>
+        <v>122.5422</v>
       </c>
       <c r="J28" s="13" t="n">
         <v>0</v>
@@ -1411,22 +1411,22 @@
       <c r="B29" s="15" t="n"/>
       <c r="C29" s="16" t="n"/>
       <c r="D29" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>116.25</v>
+        <v>154.4172</v>
       </c>
       <c r="H29" s="18" t="n">
         <v>100</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>16.25</v>
+        <v>54.4172</v>
       </c>
       <c r="J29" s="18" t="n">
         <v>0</v>
@@ -1435,7 +1435,7 @@
     <row r="30" ht="13" customHeight="1">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>ОсОО «Ала-Тоо Агро»</t>
+          <t>ОсОО «Ала-Арча Энерго»</t>
         </is>
       </c>
       <c r="B30" s="20" t="n"/>
@@ -1448,13 +1448,13 @@
         <v>1</v>
       </c>
       <c r="G30" s="24" t="n">
-        <v>116.25</v>
+        <v>38.1672</v>
       </c>
       <c r="H30" s="24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="24" t="n">
-        <v>16.25</v>
+        <v>38.1672</v>
       </c>
       <c r="J30" s="24" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="25" t="inlineStr">
         <is>
-          <t>№ 25-4/030 от 10.02.2025, KGS</t>
+          <t>№ 21-9/040 от 20.09.2021, EUR</t>
         </is>
       </c>
       <c r="B31" s="20" t="n"/>
@@ -1474,13 +1474,13 @@
         <v>1</v>
       </c>
       <c r="G31" s="24" t="n">
-        <v>116.25</v>
+        <v>38.1672</v>
       </c>
       <c r="H31" s="24" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I31" s="24" t="n">
-        <v>16.25</v>
+        <v>38.1672</v>
       </c>
       <c r="J31" s="24" t="n">
         <v>0</v>
@@ -1489,11 +1489,11 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="26" t="inlineStr">
         <is>
-          <t>п/п 4388</t>
+          <t>п/п 4431</t>
         </is>
       </c>
       <c r="B32" s="27" t="n">
-        <v>46275</v>
+        <v>46286</v>
       </c>
       <c r="C32" s="28" t="inlineStr">
         <is>
@@ -1504,587 +1504,671 @@
       <c r="E32" s="29" t="n"/>
       <c r="F32" s="29" t="n"/>
       <c r="G32" s="30" t="n">
+        <v>38.1672</v>
+      </c>
+      <c r="H32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="30" t="n">
+        <v>38.1672</v>
+      </c>
+      <c r="J32" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="13" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>ОсОО «Ала-Тоо Агро»</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="n"/>
+      <c r="C33" s="21" t="n"/>
+      <c r="D33" s="22" t="n"/>
+      <c r="E33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="24" t="n">
         <v>116.25</v>
       </c>
-      <c r="H32" s="30" t="n">
+      <c r="H33" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="I32" s="30" t="n">
+      <c r="I33" s="24" t="n">
         <v>16.25</v>
       </c>
-      <c r="J32" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>г. Кара-Балта</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" s="18" t="n">
-        <v>65</v>
-      </c>
-      <c r="H33" s="18" t="n">
-        <v>50</v>
-      </c>
-      <c r="I33" s="18" t="n">
-        <v>15</v>
-      </c>
-      <c r="J33" s="18" t="n">
+      <c r="J33" s="24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>ОсОО «Кара-Балта Мел»</t>
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>№ 25-4/030 от 10.02.2025, KGS</t>
         </is>
       </c>
       <c r="B34" s="20" t="n"/>
       <c r="C34" s="21" t="n"/>
       <c r="D34" s="22" t="n"/>
-      <c r="E34" s="23" t="n">
-        <v>1</v>
-      </c>
+      <c r="E34" s="22" t="n"/>
       <c r="F34" s="23" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="24" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="H34" s="24" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="J34" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>п/п 4388</t>
+        </is>
+      </c>
+      <c r="B35" s="27" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C35" s="28" t="inlineStr">
+        <is>
+          <t>денежные средства</t>
+        </is>
+      </c>
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="29" t="n"/>
+      <c r="F35" s="29" t="n"/>
+      <c r="G35" s="30" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="H35" s="30" t="n">
+        <v>100</v>
+      </c>
+      <c r="I35" s="30" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="J35" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>г. Кара-Балта</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="18" t="n">
         <v>65</v>
       </c>
-      <c r="H34" s="24" t="n">
+      <c r="H36" s="18" t="n">
         <v>50</v>
       </c>
-      <c r="I34" s="24" t="n">
+      <c r="I36" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="J34" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="J36" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>ОсОО «Кара-Балта Мел»</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="n"/>
+      <c r="C37" s="21" t="n"/>
+      <c r="D37" s="22" t="n"/>
+      <c r="E37" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="24" t="n">
+        <v>65</v>
+      </c>
+      <c r="H37" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="I37" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="J37" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="25" t="inlineStr">
         <is>
           <t>№ 20-2/090 от 12.08.2020, KGS</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="n"/>
-      <c r="C35" s="21" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="22" t="n"/>
-      <c r="F35" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" s="24" t="n">
-        <v>65</v>
-      </c>
-      <c r="H35" s="24" t="n">
-        <v>50</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <v>15</v>
-      </c>
-      <c r="J35" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="26" t="inlineStr">
-        <is>
-          <t>п/п 4402</t>
-        </is>
-      </c>
-      <c r="B36" s="27" t="n">
-        <v>46277</v>
-      </c>
-      <c r="C36" s="28" t="inlineStr">
-        <is>
-          <t>денежные средства</t>
-        </is>
-      </c>
-      <c r="D36" s="29" t="n"/>
-      <c r="E36" s="29" t="n"/>
-      <c r="F36" s="29" t="n"/>
-      <c r="G36" s="30" t="n">
-        <v>65</v>
-      </c>
-      <c r="H36" s="30" t="n">
-        <v>50</v>
-      </c>
-      <c r="I36" s="30" t="n">
-        <v>15</v>
-      </c>
-      <c r="J36" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="14" t="inlineStr">
-        <is>
-          <t>Сокулукский р-н</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="F37" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" s="18" t="n">
-        <v>283.125</v>
-      </c>
-      <c r="H37" s="18" t="n">
-        <v>230</v>
-      </c>
-      <c r="I37" s="18" t="n">
-        <v>53.125</v>
-      </c>
-      <c r="J37" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="13" customHeight="1">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>ОсОО «Ак-Дан»</t>
         </is>
       </c>
       <c r="B38" s="20" t="n"/>
       <c r="C38" s="21" t="n"/>
       <c r="D38" s="22" t="n"/>
-      <c r="E38" s="23" t="n">
+      <c r="E38" s="22" t="n"/>
+      <c r="F38" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="24" t="n">
+        <v>65</v>
+      </c>
+      <c r="H38" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="I38" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="J38" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>п/п 4402</t>
+        </is>
+      </c>
+      <c r="B39" s="27" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C39" s="28" t="inlineStr">
+        <is>
+          <t>денежные средства</t>
+        </is>
+      </c>
+      <c r="D39" s="29" t="n"/>
+      <c r="E39" s="29" t="n"/>
+      <c r="F39" s="29" t="n"/>
+      <c r="G39" s="30" t="n">
+        <v>65</v>
+      </c>
+      <c r="H39" s="30" t="n">
+        <v>50</v>
+      </c>
+      <c r="I39" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="J39" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="13" customHeight="1">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>Сокулукский р-н</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="23" t="n">
+      <c r="F40" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G38" s="24" t="n">
+      <c r="G40" s="18" t="n">
         <v>283.125</v>
       </c>
-      <c r="H38" s="24" t="n">
+      <c r="H40" s="18" t="n">
         <v>230</v>
       </c>
-      <c r="I38" s="24" t="n">
+      <c r="I40" s="18" t="n">
         <v>53.125</v>
       </c>
-      <c r="J38" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="25" t="inlineStr">
-        <is>
-          <t>№ 21-3/117 от 15.04.2021, KGS</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="n"/>
-      <c r="C39" s="21" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="22" t="n"/>
-      <c r="F39" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="24" t="n">
-        <v>170.625</v>
-      </c>
-      <c r="H39" s="24" t="n">
-        <v>130</v>
-      </c>
-      <c r="I39" s="24" t="n">
-        <v>40.625</v>
-      </c>
-      <c r="J39" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="13" customHeight="1">
-      <c r="A40" s="26" t="inlineStr">
-        <is>
-          <t>п/п 4417</t>
-        </is>
-      </c>
-      <c r="B40" s="27" t="n">
-        <v>46280</v>
-      </c>
-      <c r="C40" s="28" t="inlineStr">
-        <is>
-          <t>денежные средства</t>
-        </is>
-      </c>
-      <c r="D40" s="29" t="n"/>
-      <c r="E40" s="29" t="n"/>
-      <c r="F40" s="29" t="n"/>
-      <c r="G40" s="30" t="n">
-        <v>170.625</v>
-      </c>
-      <c r="H40" s="30" t="n">
-        <v>130</v>
-      </c>
-      <c r="I40" s="30" t="n">
-        <v>40.625</v>
-      </c>
-      <c r="J40" s="30" t="n">
+      <c r="J40" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41" ht="13" customHeight="1">
-      <c r="A41" s="25" t="inlineStr">
-        <is>
-          <t>№ 22-2/031 от 11.03.2022, KGS</t>
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>ОсОО «Ак-Дан»</t>
         </is>
       </c>
       <c r="B41" s="20" t="n"/>
       <c r="C41" s="21" t="n"/>
       <c r="D41" s="22" t="n"/>
-      <c r="E41" s="22" t="n"/>
+      <c r="E41" s="23" t="n">
+        <v>2</v>
+      </c>
       <c r="F41" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G41" s="24" t="n">
+        <v>283.125</v>
+      </c>
+      <c r="H41" s="24" t="n">
+        <v>230</v>
+      </c>
+      <c r="I41" s="24" t="n">
+        <v>53.125</v>
+      </c>
+      <c r="J41" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="13" customHeight="1">
+      <c r="A42" s="25" t="inlineStr">
+        <is>
+          <t>№ 21-3/117 от 15.04.2021, KGS</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n"/>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="22" t="n"/>
+      <c r="E42" s="22" t="n"/>
+      <c r="F42" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="24" t="n">
+        <v>170.625</v>
+      </c>
+      <c r="H42" s="24" t="n">
+        <v>130</v>
+      </c>
+      <c r="I42" s="24" t="n">
+        <v>40.625</v>
+      </c>
+      <c r="J42" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="26" t="inlineStr">
+        <is>
+          <t>п/п 4417</t>
+        </is>
+      </c>
+      <c r="B43" s="27" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C43" s="28" t="inlineStr">
+        <is>
+          <t>денежные средства</t>
+        </is>
+      </c>
+      <c r="D43" s="29" t="n"/>
+      <c r="E43" s="29" t="n"/>
+      <c r="F43" s="29" t="n"/>
+      <c r="G43" s="30" t="n">
+        <v>170.625</v>
+      </c>
+      <c r="H43" s="30" t="n">
+        <v>130</v>
+      </c>
+      <c r="I43" s="30" t="n">
+        <v>40.625</v>
+      </c>
+      <c r="J43" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="13" customHeight="1">
+      <c r="A44" s="25" t="inlineStr">
+        <is>
+          <t>№ 22-2/031 от 11.03.2022, KGS</t>
+        </is>
+      </c>
+      <c r="B44" s="20" t="n"/>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="22" t="n"/>
+      <c r="E44" s="22" t="n"/>
+      <c r="F44" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="24" t="n">
         <v>112.5</v>
       </c>
-      <c r="H41" s="24" t="n">
+      <c r="H44" s="24" t="n">
         <v>100</v>
       </c>
-      <c r="I41" s="24" t="n">
+      <c r="I44" s="24" t="n">
         <v>12.5</v>
       </c>
-      <c r="J41" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="13" customHeight="1">
-      <c r="A42" s="26" t="inlineStr">
+      <c r="J44" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>п/п 4398</t>
         </is>
       </c>
-      <c r="B42" s="27" t="n">
+      <c r="B45" s="27" t="n">
         <v>46276</v>
       </c>
-      <c r="C42" s="28" t="inlineStr">
+      <c r="C45" s="28" t="inlineStr">
         <is>
           <t>денежные средства</t>
         </is>
       </c>
-      <c r="D42" s="29" t="n"/>
-      <c r="E42" s="29" t="n"/>
-      <c r="F42" s="29" t="n"/>
-      <c r="G42" s="30" t="n">
+      <c r="D45" s="29" t="n"/>
+      <c r="E45" s="29" t="n"/>
+      <c r="F45" s="29" t="n"/>
+      <c r="G45" s="30" t="n">
         <v>112.5</v>
       </c>
-      <c r="H42" s="30" t="n">
+      <c r="H45" s="30" t="n">
         <v>100</v>
       </c>
-      <c r="I42" s="30" t="n">
+      <c r="I45" s="30" t="n">
         <v>12.5</v>
       </c>
-      <c r="J42" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="13" customHeight="1">
-      <c r="A43" s="10" t="inlineStr">
+      <c r="J45" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="10" t="inlineStr">
         <is>
           <t>г. Бишкек</t>
         </is>
       </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="13" t="n">
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" s="13" t="n">
         <v>461.035</v>
       </c>
-      <c r="H43" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>437</v>
       </c>
-      <c r="I43" s="13" t="n">
+      <c r="I46" s="13" t="n">
         <v>24.035</v>
       </c>
-      <c r="J43" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="13" customHeight="1">
-      <c r="A44" s="14" t="inlineStr">
+      <c r="J46" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="14" t="inlineStr">
         <is>
           <t>г. Бишкек</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n"/>
-      <c r="C44" s="16" t="n"/>
-      <c r="D44" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" s="18" t="n">
+      <c r="B47" s="15" t="n"/>
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="18" t="n">
         <v>461.035</v>
       </c>
-      <c r="H44" s="18" t="n">
+      <c r="H47" s="18" t="n">
         <v>437</v>
       </c>
-      <c r="I44" s="18" t="n">
+      <c r="I47" s="18" t="n">
         <v>24.035</v>
       </c>
-      <c r="J44" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="13" customHeight="1">
-      <c r="A45" s="19" t="inlineStr">
+      <c r="J47" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>ОсОО «Кут-Мүлк»</t>
         </is>
       </c>
-      <c r="B45" s="20" t="n"/>
-      <c r="C45" s="21" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="24" t="n">
+      <c r="B48" s="20" t="n"/>
+      <c r="C48" s="21" t="n"/>
+      <c r="D48" s="22" t="n"/>
+      <c r="E48" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G48" s="24" t="n">
         <v>461.035</v>
       </c>
-      <c r="H45" s="24" t="n">
+      <c r="H48" s="24" t="n">
         <v>437</v>
       </c>
-      <c r="I45" s="24" t="n">
+      <c r="I48" s="24" t="n">
         <v>24.035</v>
       </c>
-      <c r="J45" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="13" customHeight="1">
-      <c r="A46" s="25" t="inlineStr">
+      <c r="J48" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>№ 23-1/019 от 05.05.2023, USD</t>
         </is>
       </c>
-      <c r="B46" s="20" t="n"/>
-      <c r="C46" s="21" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="22" t="n"/>
-      <c r="F46" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="24" t="n">
+      <c r="B49" s="20" t="n"/>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="22" t="n"/>
+      <c r="E49" s="22" t="n"/>
+      <c r="F49" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="24" t="n">
         <v>461.035</v>
       </c>
-      <c r="H46" s="24" t="n">
+      <c r="H49" s="24" t="n">
         <v>437</v>
       </c>
-      <c r="I46" s="24" t="n">
+      <c r="I49" s="24" t="n">
         <v>24.035</v>
       </c>
-      <c r="J46" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="26" t="inlineStr">
+      <c r="J49" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="26" t="inlineStr">
         <is>
           <t>п/п 4372</t>
         </is>
       </c>
-      <c r="B47" s="27" t="n">
+      <c r="B50" s="27" t="n">
         <v>46270</v>
       </c>
-      <c r="C47" s="28" t="inlineStr">
+      <c r="C50" s="28" t="inlineStr">
         <is>
           <t>денежные средства</t>
         </is>
       </c>
-      <c r="D47" s="29" t="n"/>
-      <c r="E47" s="29" t="n"/>
-      <c r="F47" s="29" t="n"/>
-      <c r="G47" s="30" t="n">
+      <c r="D50" s="29" t="n"/>
+      <c r="E50" s="29" t="n"/>
+      <c r="F50" s="29" t="n"/>
+      <c r="G50" s="30" t="n">
         <v>461.035</v>
       </c>
-      <c r="H47" s="30" t="n">
+      <c r="H50" s="30" t="n">
         <v>437</v>
       </c>
-      <c r="I47" s="30" t="n">
+      <c r="I50" s="30" t="n">
         <v>24.035</v>
       </c>
-      <c r="J47" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="13" customHeight="1">
-      <c r="A48" s="10" t="inlineStr">
+      <c r="J50" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
         <is>
           <t>г. Ош</t>
         </is>
       </c>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" s="13" t="n">
+      <c r="B51" s="11" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="13" t="n">
         <v>520</v>
       </c>
-      <c r="H48" s="13" t="n">
+      <c r="H51" s="13" t="n">
         <v>500</v>
       </c>
-      <c r="I48" s="13" t="n">
+      <c r="I51" s="13" t="n">
         <v>20</v>
       </c>
-      <c r="J48" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="13" customHeight="1">
-      <c r="A49" s="14" t="inlineStr">
+      <c r="J51" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="14" t="inlineStr">
         <is>
           <t>г. Ош</t>
         </is>
       </c>
-      <c r="B49" s="15" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="18" t="n">
+      <c r="B52" s="15" t="n"/>
+      <c r="C52" s="16" t="n"/>
+      <c r="D52" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="18" t="n">
         <v>520</v>
       </c>
-      <c r="H49" s="18" t="n">
+      <c r="H52" s="18" t="n">
         <v>500</v>
       </c>
-      <c r="I49" s="18" t="n">
+      <c r="I52" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="J49" s="18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="19" t="inlineStr">
+      <c r="J52" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>ОсОО «Ош-Нан»</t>
         </is>
       </c>
-      <c r="B50" s="20" t="n"/>
-      <c r="C50" s="21" t="n"/>
-      <c r="D50" s="22" t="n"/>
-      <c r="E50" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="24" t="n">
+      <c r="B53" s="20" t="n"/>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="22" t="n"/>
+      <c r="E53" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" s="24" t="n">
         <v>520</v>
       </c>
-      <c r="H50" s="24" t="n">
+      <c r="H53" s="24" t="n">
         <v>500</v>
       </c>
-      <c r="I50" s="24" t="n">
+      <c r="I53" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="J50" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="25" t="inlineStr">
+      <c r="J53" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="25" t="inlineStr">
         <is>
           <t>№ 20-1/412 от 14.10.2020, KGS</t>
         </is>
       </c>
-      <c r="B51" s="20" t="n"/>
-      <c r="C51" s="21" t="n"/>
-      <c r="D51" s="22" t="n"/>
-      <c r="E51" s="22" t="n"/>
-      <c r="F51" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="24" t="n">
+      <c r="B54" s="20" t="n"/>
+      <c r="C54" s="21" t="n"/>
+      <c r="D54" s="22" t="n"/>
+      <c r="E54" s="22" t="n"/>
+      <c r="F54" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" s="24" t="n">
         <v>520</v>
       </c>
-      <c r="H51" s="24" t="n">
+      <c r="H54" s="24" t="n">
         <v>500</v>
       </c>
-      <c r="I51" s="24" t="n">
+      <c r="I54" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="J51" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="26" t="inlineStr">
+      <c r="J54" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="26" t="inlineStr">
         <is>
           <t>п/п 3096</t>
         </is>
       </c>
-      <c r="B52" s="27" t="n">
+      <c r="B55" s="27" t="n">
         <v>46283</v>
       </c>
-      <c r="C52" s="28" t="inlineStr">
+      <c r="C55" s="28" t="inlineStr">
         <is>
           <t>денежные средства</t>
         </is>
       </c>
-      <c r="D52" s="29" t="n"/>
-      <c r="E52" s="29" t="n"/>
-      <c r="F52" s="29" t="n"/>
-      <c r="G52" s="30" t="n">
+      <c r="D55" s="29" t="n"/>
+      <c r="E55" s="29" t="n"/>
+      <c r="F55" s="29" t="n"/>
+      <c r="G55" s="30" t="n">
         <v>520</v>
       </c>
-      <c r="H52" s="30" t="n">
+      <c r="H55" s="30" t="n">
         <v>500</v>
       </c>
-      <c r="I52" s="30" t="n">
+      <c r="I55" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="J52" s="30" t="n">
+      <c r="J55" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2266,7 +2350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2404,28 +2488,28 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>1667.91</v>
+        <v>1706.0772</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>1467</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>200.91</v>
+        <v>239.0772</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>17067.35003</v>
+        <v>18638.16683</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>9572.9</v>
+        <v>11147.71557</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
@@ -2700,7 +2784,7 @@
     <row r="18" ht="13" customHeight="1">
       <c r="A18" s="40" t="inlineStr">
         <is>
-          <t>ОсОО «Эко-Продукт»</t>
+          <t>ОсОО «Ысык-Көл Логистик»</t>
         </is>
       </c>
       <c r="B18" s="29" t="n"/>
@@ -2762,28 +2846,28 @@
         </is>
       </c>
       <c r="B20" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C20" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D20" s="36" t="n">
-        <v>809.16</v>
+        <v>847.3271999999999</v>
       </c>
       <c r="E20" s="36" t="n">
         <v>717</v>
       </c>
       <c r="F20" s="36" t="n">
-        <v>92.16</v>
+        <v>130.3272</v>
       </c>
       <c r="G20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="36" t="n">
-        <v>11746.1</v>
+        <v>13316.9168</v>
       </c>
       <c r="I20" s="36" t="n">
-        <v>6476.9</v>
+        <v>8051.71557</v>
       </c>
     </row>
     <row r="21" ht="13" customHeight="1">
@@ -2793,28 +2877,28 @@
         </is>
       </c>
       <c r="B21" s="38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" s="38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="39" t="n">
-        <v>461.035</v>
+        <v>499.2022</v>
       </c>
       <c r="E21" s="39" t="n">
         <v>437</v>
       </c>
       <c r="F21" s="39" t="n">
-        <v>24.035</v>
+        <v>62.2022</v>
       </c>
       <c r="G21" s="39" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="39" t="n">
-        <v>8477.975</v>
+        <v>10048.7918</v>
       </c>
       <c r="I21" s="39" t="n">
-        <v>3862.4</v>
+        <v>5437.21557</v>
       </c>
     </row>
     <row r="22" ht="13" customHeight="1">
@@ -2849,118 +2933,147 @@
     <row r="23" ht="13" customHeight="1">
       <c r="A23" s="40" t="inlineStr">
         <is>
-          <t>ОАО «Бишкексүт»</t>
+          <t>ОсОО «Ала-Арча Энерго»</t>
         </is>
       </c>
       <c r="B23" s="29" t="n"/>
       <c r="C23" s="41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" s="30" t="n">
-        <v>0</v>
+        <v>38.1672</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="30" t="n">
-        <v>0</v>
+        <v>38.1672</v>
       </c>
       <c r="G23" s="30" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="30" t="n">
+        <v>1570.8168</v>
+      </c>
+      <c r="I23" s="30" t="n">
+        <v>1574.81557</v>
+      </c>
+    </row>
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>ОАО «Бишкексүт»</t>
+        </is>
+      </c>
+      <c r="B24" s="29" t="n"/>
+      <c r="C24" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="30" t="n">
         <v>4250</v>
       </c>
-      <c r="I23" s="30" t="n">
+      <c r="I24" s="30" t="n">
         <v>480</v>
       </c>
     </row>
-    <row r="24" ht="13" customHeight="1">
-      <c r="A24" s="37" t="inlineStr">
+    <row r="25" ht="13" customHeight="1">
+      <c r="A25" s="37" t="inlineStr">
         <is>
           <t>Асанов А. К.</t>
         </is>
       </c>
-      <c r="B24" s="38" t="n">
+      <c r="B25" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="38" t="n">
+      <c r="C25" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="D24" s="39" t="n">
+      <c r="D25" s="39" t="n">
         <v>348.125</v>
       </c>
-      <c r="E24" s="39" t="n">
+      <c r="E25" s="39" t="n">
         <v>280</v>
       </c>
-      <c r="F24" s="39" t="n">
+      <c r="F25" s="39" t="n">
         <v>68.125</v>
       </c>
-      <c r="G24" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="39" t="n">
+      <c r="G25" s="39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="39" t="n">
         <v>3268.125</v>
       </c>
-      <c r="I24" s="39" t="n">
+      <c r="I25" s="39" t="n">
         <v>2614.5</v>
-      </c>
-    </row>
-    <row r="25" ht="13" customHeight="1">
-      <c r="A25" s="40" t="inlineStr">
-        <is>
-          <t>ОсОО «Ак-Дан»</t>
-        </is>
-      </c>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="41" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="30" t="n">
-        <v>283.125</v>
-      </c>
-      <c r="E25" s="30" t="n">
-        <v>230</v>
-      </c>
-      <c r="F25" s="30" t="n">
-        <v>53.125</v>
-      </c>
-      <c r="G25" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="30" t="n">
-        <v>2634.375</v>
-      </c>
-      <c r="I25" s="30" t="n">
-        <v>2107.5</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="40" t="inlineStr">
         <is>
-          <t>ОсОО «Кара-Балта Мел»</t>
+          <t>ОсОО «Ак-Дан»</t>
         </is>
       </c>
       <c r="B26" s="29" t="n"/>
       <c r="C26" s="41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="30" t="n">
+        <v>283.125</v>
+      </c>
+      <c r="E26" s="30" t="n">
+        <v>230</v>
+      </c>
+      <c r="F26" s="30" t="n">
+        <v>53.125</v>
+      </c>
+      <c r="G26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="30" t="n">
+        <v>2634.375</v>
+      </c>
+      <c r="I26" s="30" t="n">
+        <v>2107.5</v>
+      </c>
+    </row>
+    <row r="27" ht="13" customHeight="1">
+      <c r="A27" s="40" t="inlineStr">
+        <is>
+          <t>ОсОО «Кара-Балта Мел»</t>
+        </is>
+      </c>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="30" t="n">
         <v>65</v>
       </c>
-      <c r="E26" s="30" t="n">
+      <c r="E27" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="F26" s="30" t="n">
+      <c r="F27" s="30" t="n">
         <v>15</v>
       </c>
-      <c r="G26" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="30" t="n">
+      <c r="G27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="30" t="n">
         <v>633.75</v>
       </c>
-      <c r="I26" s="30" t="n">
+      <c r="I27" s="30" t="n">
         <v>507</v>
       </c>
     </row>
@@ -3153,7 +3266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3303,7 +3416,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="300" customHeight="1">
+    <row r="14" ht="330" customHeight="1">
       <c r="A14" s="43" t="inlineStr">
         <is>
           <t>Строки</t>
@@ -3311,7 +3424,7 @@
       </c>
       <c r="B14" s="44" t="inlineStr">
         <is>
-          <t>Строка детали — платёж: номер платёжного документа («п/п 4372»), дата платежа и вид погашения. В отчёт попадают платежи с датой поступления в периоде, засчитанные в погашение так же, как в расчёте кредита: подтверждённые Центральным казначейством, восстановленные, с расхождением — по сумме ЦК, поступившие через шлюз и ещё ожидающие подтверждения. Сторнированные и внесённые вручную или импортом, но не подтверждённые ЦК, не входят. Дата платежа — дата фактического поступления денег: поступление, опознанное позже, ложится в свой день, поэтому до закрытия периода отчёт за него может меняться. Принятие имущества в счёт погашения — платёж с этим видом погашения. Не погашения и в отчёт не входят: списание (ФО-11), перевод долга, доля залогодателя в выручке от реализации залога, невыясненные поступления, возврат переплаты. «Всего погашено» = основная сумма + проценты (вместе с накопленными) + штрафы; доля платежа на расходы по взысканию в отчёт не входит. Над платежами разрезы, по умолчанию область → район → заёмщик → кредит; строка кредита («№ … от …, KGS») есть всегда, даже при одном платеже; у городов республиканского значения — обе строки, области и района. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Порядок: области — по справочнику (области по алфавиту, затем г. Бишкек, г. Ош); районы — по алфавиту; заёмщики — по алфавиту; кредиты заёмщика — по дате договора; платежи кредита — по дате платежа, от ранних к поздним. Суммы — только в сомах (тыс. сом), в том числе по кредитам в иностранной валюте: погашения приходят в сомах, в валюту договора их пересчитывает расчёт задолженности; строки в валюте нет. Колонок сравнения с другими периодами нет: с начала года — выбором периода, помесячно — разрезом «Месяц». Печать — A4 альбомная в одну страницу по ширине.</t>
+          <t>Строка детали — платёж: номер платёжного документа («п/п 4372»), дата платежа и вид погашения. В отчёт попадают платежи с датой поступления в периоде, засчитанные в погашение так же, как в расчёте кредита: подтверждённые Центральным казначейством, восстановленные, с расхождением — по сумме ЦК, поступившие через шлюз и ещё ожидающие подтверждения. Сторнированные и внесённые вручную или импортом, но не подтверждённые ЦК, не входят. Дата платежа — дата фактического поступления денег: поступление, опознанное позже, ложится в свой день, поэтому до закрытия периода отчёт за него может меняться. Принятие имущества в счёт погашения — платёж с этим видом погашения. Не погашения и в отчёт не входят: списание (ФО-11), перевод долга, доля залогодателя в выручке от реализации залога, невыясненные поступления, возврат переплаты. «Всего погашено» = основная сумма + проценты (вместе с накопленными) + штрафы; доля платежа на расходы по взысканию в отчёт не входит. Заёмщик, департамент и куратор — на последний день периода, как ФО-05 и ФО-54: после перевода долга кредит и все его платежи, в том числе внесённые прежним заёмщиком, — под новым заёмщиком, отбор по заёмщику находит и прежнего; область и район — кредита (на подтверждение). Над платежами разрезы, по умолчанию область → район → заёмщик → кредит; строка кредита («№ … от …, KGS») есть всегда, даже при одном платеже; у городов республиканского значения — обе строки, области и района. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Порядок: области — по справочнику (области по алфавиту, затем г. Бишкек, г. Ош); районы — по алфавиту; заёмщики — по алфавиту; кредиты заёмщика — по дате договора; платежи кредита — по дате платежа, от ранних к поздним. Суммы — только в сомах (тыс. сом), в том числе по кредитам в иностранной валюте: погашения приходят в сомах, в валюту договора их пересчитывает расчёт задолженности; строки в валюте нет. Колонок сравнения с другими периодами нет: с начала года — выбором периода, помесячно — разрезом «Месяц». Печать — A4 альбомная в одну страницу по ширине.</t>
         </is>
       </c>
     </row>
@@ -3532,7 +3645,7 @@
       </c>
       <c r="B33" s="44" t="inlineStr">
         <is>
-          <t>За сентябрь 2026: 9 заёмщиков, 10 кредитов, 10 платежей; «Всего погашено» 1 667,910 тыс. сом, в том числе основная сумма 1 467,000, проценты 200,910, штрафы 0,000.</t>
+          <t>За сентябрь 2026: 10 заёмщиков, 11 кредитов, 11 платежей; «Всего погашено» 1 706,077 тыс. сом, в том числе основная сумма 1 467,000, проценты 239,077, штрафы 0,000.</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3709,7 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
+    <row r="39" ht="75" customHeight="1">
       <c r="A39" s="43" t="inlineStr">
         <is>
           <t>7.</t>
@@ -3604,11 +3717,11 @@
       </c>
       <c r="B39" s="44" t="inlineStr">
         <is>
-          <t>Платёж КЗ-15 от 18.09.2026 (полное погашение, 520,000) в отчёте есть, хотя на 01.10.2026 кредит закрыт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
+          <t>Платёж КЗ-25 № 21-9/040 по кредиту в евро (срок 20.09.2026 — воскресенье, перенесён на 21.09.2026): п/п 4431 от 21.09.2026 — только проценты за 21.08–20.09.2026, 376,96 EUR = 38,167 тыс. сом, как поступили (38 167,20 сом по курсу 101,25 на день платежа); основной суммы в сентябре нет. ФО-05 и ФО-54 берут тот же платёж по курсу 30.09.2026 — 38,261 (376,96 EUR × 101,50); разница 0,094 — курсовая.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="43" t="inlineStr">
         <is>
           <t>8.</t>
@@ -3616,7 +3729,7 @@
       </c>
       <c r="B40" s="44" t="inlineStr">
         <is>
-          <t>Платёж КЗ-07 от 02.09.2026 показан; перевод его долга 09.09.2026 и списание КЗ-08 17.09.2026 (ФО-11) — не платежи и не показаны.</t>
+          <t>Сверка сентября 2026: ИТОГО 1 706,077 = «Погашено — всего» ФО-54 1 706,699 − курсовая разница валютных платежей 0,622 (КЗ-11 0,528, КЗ-25 0,094) = «Оплачено» ФО-05 1 456,699 + досрочное погашение КЗ-15 сверх графика 250,000 − 0,622. «По основной сумме» платежей по валютным кредитам 437,000 (только КЗ-11) = «погашено» ФО-53 за сентябрь.</t>
         </is>
       </c>
     </row>
@@ -3628,72 +3741,96 @@
       </c>
       <c r="B41" s="44" t="inlineStr">
         <is>
+          <t>Платёж КЗ-15 от 18.09.2026 (полное погашение, 520,000) в отчёте есть, хотя на 01.10.2026 кредит закрыт.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>10.</t>
+        </is>
+      </c>
+      <c r="B42" s="44" t="inlineStr">
+        <is>
+          <t>Платёж КЗ-07 № 21-6/144 п/п 4361 от 02.09.2026 (72,083) внёс ОсОО «Эко-Продукт», показан он под ОсОО «Ысык-Көл Логистик» — заёмщиком на 30.09.2026 (долг переведён 09.09.2026), в Иссык-Кульской обл., Тюпском р-не; сам перевод долга и списание КЗ-08 17.09.2026 (ФО-11) — не платежи и не показаны.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>11.</t>
+        </is>
+      </c>
+      <c r="B43" s="44" t="inlineStr">
+        <is>
           <t>Остальные заёмщики набора в сентябре 2026 не платили и не показаны; платёж КЗ-24 от 14.08.2026 — в отчёте за август.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="43" t="inlineStr">
-        <is>
-          <t>10.</t>
-        </is>
-      </c>
-      <c r="B42" s="44" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>12.</t>
+        </is>
+      </c>
+      <c r="B44" s="44" t="inlineStr">
         <is>
           <t>Отбор «вид погашения: имущество в счёт погашения» за 01.01.2026–30.09.2026 — только КЗ-16, платёж 20.03.2026 на 4 250,000 тыс. сом.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="43" t="inlineStr">
-        <is>
-          <t>11.</t>
-        </is>
-      </c>
-      <c r="B43" s="44" t="inlineStr">
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>13.</t>
+        </is>
+      </c>
+      <c r="B45" s="44" t="inlineStr">
         <is>
           <t>У г. Бишкек и г. Ош по две строки: область и район.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="45" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="45" t="inlineStr">
         <is>
           <t>Вид 1: «Собрано за месяц» — лист «Вид 1»</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="43" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="43" t="inlineStr">
         <is>
           <t>Кому и зачем</t>
         </is>
       </c>
-      <c r="B46" s="44" t="inlineStr">
+      <c r="B48" s="44" t="inlineStr">
         <is>
           <t>Руководству — сколько погашено за месяц по департаментам и кураторам и как это соотносится с тем же периодом прошлого года. Свод на одну страницу: без строк кредитов и платежей.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="43" t="inlineStr">
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="43" t="inlineStr">
         <is>
           <t>Когда</t>
         </is>
       </c>
-      <c r="B47" s="44" t="inlineStr">
+      <c r="B49" s="44" t="inlineStr">
         <is>
           <t>За календарный месяц, по требованию; по умолчанию — прошлый месяц.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="120" customHeight="1">
-      <c r="A48" s="43" t="inlineStr">
+    <row r="50" ht="120" customHeight="1">
+      <c r="A50" s="43" t="inlineStr">
         <is>
           <t>Параметры</t>
         </is>
       </c>
-      <c r="B48" s="44" t="inlineStr">
+      <c r="B50" s="44" t="inlineStr">
         <is>
           <t>• Месяц — прошлый месяц; можно выбрать любой
 • Единица — тыс. сом (можно выбрать «сом»)
@@ -3702,159 +3839,170 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="105" customHeight="1">
-      <c r="A49" s="43" t="inlineStr">
+    <row r="51" ht="105" customHeight="1">
+      <c r="A51" s="43" t="inlineStr">
         <is>
           <t>Строки</t>
         </is>
       </c>
-      <c r="B49" s="44" t="inlineStr">
+      <c r="B51" s="44" t="inlineStr">
         <is>
           <t>Те же платежи, что в отчёте (засчитанные в погашение, по дате поступления), сведены до заёмщика: строка детали — заёмщик, строк кредитов и платежей нет. Над заёмщиками разрезы, по умолчанию департамент → куратор. Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Строки — заёмщики, у которых есть платежи за месяц, с начала года или за тот же период прошлого года; заёмщик без платежей в месяце стоит с 0,00 в колонках месяца. Порядок на каждом уровне — по убыванию «Всего погашено» за месяц, при равенстве — по убыванию «С начала года». Суммы — только в сомах (тыс. сом). Печать — A4 альбомная в одну страницу по ширине.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="43" t="inlineStr">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="43" t="inlineStr">
         <is>
           <t>Разрезы</t>
         </is>
       </c>
-      <c r="B50" s="44" t="inlineStr">
+      <c r="B52" s="44" t="inlineStr">
         <is>
           <t>по умолчанию: Департамент → Куратор → заёмщик; можно выбрать: Область, Район, Айыл окмоту, Село, Департамент, Отдел, Куратор, Отрасль, Вид кредита, Кредитная линия, Валюта, Вид погашения</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="43" t="inlineStr">
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="43" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="B51" s="44" t="inlineStr">
+      <c r="B53" s="44" t="inlineStr">
         <is>
           <t>ТЗ 14</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="43" t="inlineStr">
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="43" t="inlineStr">
         <is>
           <t>Образец-основа</t>
         </is>
       </c>
-      <c r="B52" s="44" t="inlineStr">
+      <c r="B54" s="44" t="inlineStr">
         <is>
           <t>нет</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="43" t="inlineStr">
-        <is>
-          <t>Колонки</t>
-        </is>
-      </c>
-      <c r="B53" s="44" t="inlineStr">
-        <is>
-          <t>Наименование; Заёмщиков; Платежей; Всего погашено; в том числе: по основной сумме; в том числе: по процентам; в том числе: по штрафам; С начала года; С начала года — прошлый год</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="43" t="inlineStr">
-        <is>
-          <t>Проверка 1</t>
-        </is>
-      </c>
-      <c r="B54" s="44" t="inlineStr">
-        <is>
-          <t>За сентябрь 2026: ИТОГО — 9 заёмщиков, 10 платежей, «Всего погашено» 1 667,910 тыс. сом = ИТОГО ФО-04 за 01.09.2026–30.09.2026; основная сумма 1 467,000, проценты 200,910, штрафы 0,000.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="43" t="inlineStr">
         <is>
-          <t>Проверка 2</t>
+          <t>Колонки</t>
         </is>
       </c>
       <c r="B55" s="44" t="inlineStr">
         <is>
-          <t>«С начала года» каждой строки = «Всего погашено» ФО-04 за 01.01.2026–30.09.2026 по тому же заёмщику или разрезу; «С начала года — прошлый год» = то же за 01.01.2025–30.09.2025.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
+          <t>Наименование; Заёмщиков; Платежей; Всего погашено; в том числе: по основной сумме; в том числе: по процентам; в том числе: по штрафам; С начала года; С начала года — прошлый год</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
       <c r="A56" s="43" t="inlineStr">
         <is>
-          <t>Проверка 3</t>
+          <t>Проверка 1</t>
         </is>
       </c>
       <c r="B56" s="44" t="inlineStr">
         <is>
-          <t>Строка разреза = сумма строк на уровень ниже по каждой сумме и счётчику.</t>
+          <t>За сентябрь 2026: ИТОГО — 10 заёмщиков, 11 платежей, «Всего погашено» 1 706,077 тыс. сом = ИТОГО ФО-04 за 01.09.2026–30.09.2026; основная сумма 1 467,000, проценты 239,077, штрафы 0,000.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="43" t="inlineStr">
         <is>
-          <t>Проверка 4</t>
+          <t>Проверка 2</t>
         </is>
       </c>
       <c r="B57" s="44" t="inlineStr">
         <is>
-          <t>КЗ-16 «Бишкексүт» (имуществом 20.03.2026, 4 250,000) и КЗ-24 «Ак-Суу» (платёж 14.08.2026) в сентябре не платили — стоят строками с 0,00 за месяц и в «Заёмщиков» не считаются.</t>
+          <t>«С начала года» каждой строки = «Всего погашено» ФО-04 за 01.01.2026–30.09.2026 по тому же заёмщику или разрезу; «С начала года — прошлый год» = то же за 01.01.2025–30.09.2025.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="43" t="inlineStr">
         <is>
+          <t>Проверка 3</t>
+        </is>
+      </c>
+      <c r="B58" s="44" t="inlineStr">
+        <is>
+          <t>Строка разреза = сумма строк на уровень ниже по каждой сумме и счётчику.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="43" t="inlineStr">
+        <is>
+          <t>Проверка 4</t>
+        </is>
+      </c>
+      <c r="B59" s="44" t="inlineStr">
+        <is>
+          <t>КЗ-16 «Бишкексүт» (имуществом 20.03.2026, 4 250,000) и КЗ-24 «Ак-Суу» (платёж 14.08.2026) в сентябре не платили — стоят строками с 0,00 за месяц и в «Заёмщиков» не считаются.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="43" t="inlineStr">
+        <is>
           <t>Проверка 5</t>
         </is>
       </c>
-      <c r="B58" s="44" t="inlineStr">
+      <c r="B60" s="44" t="inlineStr">
         <is>
           <t>У КЗ-01 «Ак-Дан» два платежа за месяц по двум кредитам: «Платежей» — 2, строка одна.</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="43" t="inlineStr">
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="43" t="inlineStr">
         <is>
           <t>Проверка 6</t>
         </is>
       </c>
-      <c r="B59" s="44" t="inlineStr">
-        <is>
-          <t>Списание КЗ-08 и перевод долга КЗ-07 не платежи и в суммы не входят.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="43" t="inlineStr">
+      <c r="B61" s="44" t="inlineStr">
+        <is>
+          <t>Списание КЗ-08 и перевод долга КЗ-07 не платежи и в суммы не входят; платёж КЗ-07 от 02.09.2026 (72,083) — в строке ОсОО «Ысык-Көл Логистик», заёмщика на 30.09.2026, как в отчёте.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="30" customHeight="1">
+      <c r="A62" s="43" t="inlineStr">
         <is>
           <t>Проверка 7</t>
         </is>
       </c>
-      <c r="B60" s="44" t="inlineStr">
-        <is>
-          <t>История платежей до сентября 2026 в контрольном наборе задана только у КЗ-16; остальные суммы колонок «С начала года» в образце — для вида формы и на приёмке сверяются по правилу 2.</t>
+      <c r="B62" s="44" t="inlineStr">
+        <is>
+          <t>Под Бековой Н. С.: «Кут-Мүлк» 461,035, «Ала-Арча Энерго» 38,167 (КЗ-25, проценты 21.09.2026, по курсу дня платежа), «Бишкексүт» 0,00 — по убыванию «Всего погашено».</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="75" customHeight="1">
+      <c r="A63" s="43" t="inlineStr">
+        <is>
+          <t>Проверка 8</t>
+        </is>
+      </c>
+      <c r="B63" s="44" t="inlineStr">
+        <is>
+          <t>История платежей до сентября 2026 в контрольном наборе задана только у КЗ-16; у КЗ-25 «С начала года» — оценка по графику набора (проценты ежемесячно по 6,08 %, основная сумма 12 000,00 EUR 20.03.2026; 15 514,24 EUR по курсу 101,25 = 1 570,817), прошлый год — так же по курсу 98,00 (1 574,816); остальные суммы колонок «С начала года» в образце — для вида формы и на приёмке сверяются по правилу 2.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="41">
-    <mergeCell ref="B47:C47"/>
+  <mergeCells count="44">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B62:C62"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B46:C46"/>
     <mergeCell ref="B56:C56"/>
     <mergeCell ref="B43:C43"/>
     <mergeCell ref="B12:C12"/>
@@ -3864,6 +4012,7 @@
     <mergeCell ref="B48:C48"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B61:C61"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B60:C60"/>
     <mergeCell ref="B17:C17"/>
@@ -3872,6 +4021,7 @@
     <mergeCell ref="B53:C53"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B44:C44"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B37:C37"/>
     <mergeCell ref="B10:C10"/>
@@ -3884,8 +4034,10 @@
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B45:C45"/>
     <mergeCell ref="B36:C36"/>
     <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B63:C63"/>
     <mergeCell ref="B41:C41"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B4:C4"/>
